--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Profile</t>
   </si>
@@ -47,28 +47,52 @@
     <t>Method</t>
   </si>
   <si>
+    <t>glasgow-coma-scale-observation-profile</t>
+  </si>
+  <si>
+    <t>Glasgow Coma Scale Observation Profile</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>SNOMED CT#386557006</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
+    <t>CodeableConceptĵ</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>glasgow-coma-score-observation-profile</t>
+  </si>
+  <si>
+    <t>Glasgow Coma Score Observation Profile</t>
+  </si>
+  <si>
+    <t>SNOMED CT#248241002</t>
+  </si>
+  <si>
+    <t>integerĵ</t>
+  </si>
+  <si>
     <t>vital-sign-observation-profile</t>
   </si>
   <si>
     <t>Vital Sign Observation Profile</t>
   </si>
   <si>
-    <t>null#vital-signs</t>
-  </si>
-  <si>
-    <t/>
+    <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
     <t>http://tecnomod-um.org/ValueSet/vital-signs-vs (extensible)</t>
   </si>
   <si>
-    <t>dateTime, Period, Timing, instant</t>
-  </si>
-  <si>
     <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period, Attachment, Reference</t>
-  </si>
-  <si>
-    <t>optional</t>
   </si>
 </sst>
 </file>
@@ -202,7 +226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -251,28 +275,98 @@
         <v>13</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>14</v>
       </c>
       <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="H2" t="s" s="2">
         <v>16</v>
       </c>
-      <c r="H2" t="s" s="2">
+      <c r="I2" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="I2" t="s" s="2">
+      <c r="J2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="J2" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>14</v>
+      <c r="B3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K4" t="s" s="2">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
   <si>
     <t>Profile</t>
   </si>
@@ -78,6 +78,39 @@
   </si>
   <si>
     <t>integerĵ</t>
+  </si>
+  <si>
+    <t>highest-hyperglycemia-value-observation-profile</t>
+  </si>
+  <si>
+    <t>Highest Hyperglycemia Value Observation Profile</t>
+  </si>
+  <si>
+    <t>AnalyticsCodesCs CodeSystem#highest-hyperglycemia-value</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>highest-systolic-blood-pressure-value-observation-profile</t>
+  </si>
+  <si>
+    <t>Systolic Blood Pressure Highest Value Observation Profile</t>
+  </si>
+  <si>
+    <t>VitalSignsCs CodeSystem#highest-sys-bp</t>
+  </si>
+  <si>
+    <t>patient-ventilated-observation-profile</t>
+  </si>
+  <si>
+    <t>Patient Ventilated Observation Profile</t>
+  </si>
+  <si>
+    <t>SNOMED CT#40617009</t>
+  </si>
+  <si>
+    <t>booleanĵ</t>
   </si>
   <si>
     <t>vital-sign-observation-profile</t>
@@ -226,7 +259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -342,22 +375,22 @@
         <v>23</v>
       </c>
       <c r="C4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="F4" t="s" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>15</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>17</v>
@@ -366,6 +399,111 @@
         <v>13</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -122,7 +122,7 @@
     <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/vital-signs-vs (extensible)</t>
+    <t>http://qualityregistry.org/ValueSet/vital-signs-vs (extensible)</t>
   </si>
   <si>
     <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period, Attachment, Reference</t>
